--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,6 +1415,6915 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132586371</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>532200</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6921589</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132586319</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>532428</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6921348</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132586342</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>532450</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6921712</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>30 ex</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132586331</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>532456</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6921636</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 ex</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132586322</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97211</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>532371</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6921471</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132586358</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>532488</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6921801</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132586345</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>532451</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6921744</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132586359</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>532479</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6921806</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132586335</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>532420</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6921638</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>70 ex</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132586317</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>532572</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6921218</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132586323</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>532346</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6921473</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>25 ex</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132586364</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97211</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>532318</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6921663</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132586361</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>532468</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6921825</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>5 ex</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132586336</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>532410</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6921645</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kunde inte se med kikaren om det var både en hane och en hona. Men den ena födosökte uteslutande högt upp i träden, medan den andra var lågt ner på flera stammar. Möjligen utifrån detta att det handlar om en hane och en hona.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132586344</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>532464</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6921724</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>10 ex</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132586355</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>532518</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6921775</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132586367</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>532091</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6921651</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132586354</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80451</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>532535</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6921758</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132586332</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>532457</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6921630</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132586314</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92316</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>532567</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6921188</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132586348</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>532526</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6921737</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132586351</v>
+      </c>
+      <c r="B29" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>532556</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6921736</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132586326</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>532327</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6921455</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>140 ex</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132586316</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>532580</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6921193</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132586349</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>532533</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6921722</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132586338</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>532424</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6921684</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132586343</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>532452</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6921716</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132586370</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>532196</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6921594</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132586368</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>532092</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6921646</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132586352</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92316</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>532543</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6921755</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132586341</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>532433</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6921710</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132586374</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>532212</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6921515</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132586372</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>532266</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6921577</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132586339</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>532433</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6921682</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132586353</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>532536</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6921758</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132586313</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>532576</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6921203</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132586318</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>532537</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6921239</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132586363</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97963</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>532384</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6921694</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132586360</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>532469</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6921820</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132586357</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>532498</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6921784</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132586337</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>532410</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6921666</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132586321</v>
+      </c>
+      <c r="B49" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>532447</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6921444</v>
+      </c>
+      <c r="S49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132586329</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>532354</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6921519</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>9 ex</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132586346</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>532520</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6921725</v>
+      </c>
+      <c r="S51" t="n">
+        <v>6</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132586324</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>532330</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6921453</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132586347</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80451</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>532521</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6921732</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132586350</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>532550</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6921717</v>
+      </c>
+      <c r="S54" t="n">
+        <v>6</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>10 ex</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132586334</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>532417</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6921637</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132586328</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>532350</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6921513</v>
+      </c>
+      <c r="S56" t="n">
+        <v>7</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132586340</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>658</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>532440</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6921699</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132586369</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>532097</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6921643</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132586330</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>532342</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6921556</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132586315</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>658</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>532561</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6921190</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132586325</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>532331</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6921451</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132586375</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>532201</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6921512</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132586373</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>532239</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6921525</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2 ex</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132586377</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>532374</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6921276</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>10 ex</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132586333</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91855</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>532453</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6921617</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132586320</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>532436</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6921359</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132586365</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97211</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>532184</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6921738</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132586356</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>532498</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6921779</v>
+      </c>
+      <c r="S68" t="n">
+        <v>8</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132586366</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Flåmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>532089</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6921665</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>132586371</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,48 +1537,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132586319</v>
+        <v>132586359</v>
       </c>
       <c r="B9" t="n">
-        <v>80450</v>
+        <v>57949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532428</v>
+        <v>532479</v>
       </c>
       <c r="R9" t="n">
-        <v>6921348</v>
+        <v>6921806</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1615,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1625,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,32 +1657,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132586342</v>
+        <v>132586322</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>97219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1679,13 +1692,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532450</v>
+        <v>532371</v>
       </c>
       <c r="R10" t="n">
-        <v>6921712</v>
+        <v>6921471</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,7 +1727,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1724,12 +1737,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>30 ex</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,32 +1764,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132586331</v>
+        <v>132586358</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>80424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1791,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532456</v>
+        <v>532488</v>
       </c>
       <c r="R11" t="n">
-        <v>6921636</v>
+        <v>6921801</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1826,7 +1834,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,12 +1844,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,32 +1871,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132586322</v>
+        <v>132586345</v>
       </c>
       <c r="B12" t="n">
-        <v>97211</v>
+        <v>79319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1903,13 +1906,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532371</v>
+        <v>532451</v>
       </c>
       <c r="R12" t="n">
-        <v>6921471</v>
+        <v>6921744</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1951,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,32 +1978,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132586358</v>
+        <v>132586319</v>
       </c>
       <c r="B13" t="n">
-        <v>80422</v>
+        <v>80452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2010,13 +2013,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532488</v>
+        <v>532428</v>
       </c>
       <c r="R13" t="n">
-        <v>6921801</v>
+        <v>6921348</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2045,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,32 +2085,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132586345</v>
+        <v>132586331</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>99106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,13 +2120,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532451</v>
+        <v>532456</v>
       </c>
       <c r="R14" t="n">
-        <v>6921744</v>
+        <v>6921636</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2152,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2162,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,56 +2197,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132586359</v>
+        <v>132586342</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532479</v>
+        <v>532450</v>
       </c>
       <c r="R15" t="n">
-        <v>6921806</v>
+        <v>6921712</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,32 +2309,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132586335</v>
+        <v>132586317</v>
       </c>
       <c r="B16" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532420</v>
+        <v>532572</v>
       </c>
       <c r="R16" t="n">
-        <v>6921638</v>
+        <v>6921218</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,12 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,32 +2416,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132586317</v>
+        <v>132586335</v>
       </c>
       <c r="B17" t="n">
-        <v>91892</v>
+        <v>99106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2456,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532572</v>
+        <v>532420</v>
       </c>
       <c r="R17" t="n">
-        <v>6921218</v>
+        <v>6921638</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2496,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,7 +2531,7 @@
         <v>132586323</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,32 +2640,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132586364</v>
+        <v>132586361</v>
       </c>
       <c r="B19" t="n">
-        <v>97211</v>
+        <v>99106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532318</v>
+        <v>532468</v>
       </c>
       <c r="R19" t="n">
-        <v>6921663</v>
+        <v>6921825</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,32 +2752,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132586361</v>
+        <v>132586364</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>97219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,13 +2787,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532468</v>
+        <v>532318</v>
       </c>
       <c r="R20" t="n">
-        <v>6921825</v>
+        <v>6921663</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2817,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,12 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,7 +2862,7 @@
         <v>132586336</v>
       </c>
       <c r="B21" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>132586344</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132586355</v>
+        <v>132586367</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,37 +3106,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532518</v>
+        <v>532091</v>
       </c>
       <c r="R23" t="n">
-        <v>6921775</v>
+        <v>6921651</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3165,7 +3173,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3183,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,56 +3215,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132586367</v>
+        <v>132586354</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>80453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532091</v>
+        <v>532535</v>
       </c>
       <c r="R24" t="n">
-        <v>6921651</v>
+        <v>6921758</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3280,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3290,12 +3295,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,32 +3322,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132586354</v>
+        <v>132586355</v>
       </c>
       <c r="B25" t="n">
-        <v>80451</v>
+        <v>79319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532535</v>
+        <v>532518</v>
       </c>
       <c r="R25" t="n">
-        <v>6921758</v>
+        <v>6921775</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,7 +3432,7 @@
         <v>132586332</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>132586314</v>
       </c>
       <c r="B27" t="n">
-        <v>92316</v>
+        <v>92322</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132586348</v>
+        <v>132586349</v>
       </c>
       <c r="B28" t="n">
-        <v>80422</v>
+        <v>58110</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3667,37 +3667,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532526</v>
+        <v>532533</v>
       </c>
       <c r="R28" t="n">
-        <v>6921737</v>
+        <v>6921722</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3738,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3748,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,7 +3778,7 @@
         <v>132586351</v>
       </c>
       <c r="B29" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,32 +3882,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132586326</v>
+        <v>132586316</v>
       </c>
       <c r="B30" t="n">
-        <v>99098</v>
+        <v>79319</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3905,13 +3917,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532327</v>
+        <v>532580</v>
       </c>
       <c r="R30" t="n">
-        <v>6921455</v>
+        <v>6921193</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3940,7 +3952,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3950,12 +3962,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>140 ex</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,10 +3989,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132586316</v>
+        <v>132586338</v>
       </c>
       <c r="B31" t="n">
-        <v>79317</v>
+        <v>92197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3993,21 +4000,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,13 +4024,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532580</v>
+        <v>532424</v>
       </c>
       <c r="R31" t="n">
-        <v>6921193</v>
+        <v>6921684</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4052,7 +4059,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4062,7 +4069,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,10 +4096,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132586349</v>
+        <v>132586348</v>
       </c>
       <c r="B32" t="n">
-        <v>58109</v>
+        <v>80424</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,49 +4107,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532533</v>
+        <v>532526</v>
       </c>
       <c r="R32" t="n">
-        <v>6921722</v>
+        <v>6921737</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4171,7 +4166,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4181,7 +4176,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4208,32 +4203,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132586338</v>
+        <v>132586326</v>
       </c>
       <c r="B33" t="n">
-        <v>92191</v>
+        <v>99106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4243,10 +4238,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>532424</v>
+        <v>532327</v>
       </c>
       <c r="R33" t="n">
-        <v>6921684</v>
+        <v>6921455</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4278,7 +4273,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4288,7 +4283,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>140 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4315,32 +4315,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132586343</v>
+        <v>132586352</v>
       </c>
       <c r="B34" t="n">
-        <v>83163</v>
+        <v>92322</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>4217</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>532452</v>
+        <v>532543</v>
       </c>
       <c r="R34" t="n">
-        <v>6921716</v>
+        <v>6921755</v>
       </c>
       <c r="S34" t="n">
         <v>6</v>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4422,10 +4422,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132586370</v>
+        <v>132586343</v>
       </c>
       <c r="B35" t="n">
-        <v>57948</v>
+        <v>83165</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,45 +4433,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>532196</v>
+        <v>532452</v>
       </c>
       <c r="R35" t="n">
-        <v>6921594</v>
+        <v>6921716</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4500,7 +4492,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4510,12 +4502,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4542,10 +4529,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132586368</v>
+        <v>132586370</v>
       </c>
       <c r="B36" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,10 +4572,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532092</v>
+        <v>532196</v>
       </c>
       <c r="R36" t="n">
-        <v>6921646</v>
+        <v>6921594</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4620,7 +4607,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4630,12 +4617,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,48 +4649,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132586352</v>
+        <v>132586368</v>
       </c>
       <c r="B37" t="n">
-        <v>92316</v>
+        <v>57949</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532543</v>
+        <v>532092</v>
       </c>
       <c r="R37" t="n">
-        <v>6921755</v>
+        <v>6921646</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4732,7 +4727,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4742,7 +4737,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4772,7 +4772,7 @@
         <v>132586341</v>
       </c>
       <c r="B38" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132586374</v>
+        <v>132586372</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532212</v>
+        <v>532266</v>
       </c>
       <c r="R39" t="n">
-        <v>6921515</v>
+        <v>6921577</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4996,10 +4996,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132586372</v>
+        <v>132586374</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532266</v>
+        <v>532212</v>
       </c>
       <c r="R40" t="n">
-        <v>6921577</v>
+        <v>6921515</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132586339</v>
+        <v>132586313</v>
       </c>
       <c r="B41" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532433</v>
+        <v>532576</v>
       </c>
       <c r="R41" t="n">
-        <v>6921682</v>
+        <v>6921203</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5196,7 +5196,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5226,7 +5231,7 @@
         <v>132586353</v>
       </c>
       <c r="B42" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5330,10 +5335,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132586313</v>
+        <v>132586318</v>
       </c>
       <c r="B43" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5341,21 +5346,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,13 +5370,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>532576</v>
+        <v>532537</v>
       </c>
       <c r="R43" t="n">
-        <v>6921203</v>
+        <v>6921239</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5400,7 +5405,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,12 +5415,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5442,10 +5442,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132586318</v>
+        <v>132586339</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>91898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5453,21 +5453,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532537</v>
+        <v>532433</v>
       </c>
       <c r="R44" t="n">
-        <v>6921239</v>
+        <v>6921682</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5552,7 +5552,7 @@
         <v>132586363</v>
       </c>
       <c r="B45" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>132586360</v>
       </c>
       <c r="B46" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5776,10 +5776,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132586357</v>
+        <v>132586321</v>
       </c>
       <c r="B47" t="n">
-        <v>91892</v>
+        <v>83165</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5787,21 +5787,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5811,13 +5811,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532498</v>
+        <v>532447</v>
       </c>
       <c r="R47" t="n">
-        <v>6921784</v>
+        <v>6921444</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5883,32 +5883,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132586337</v>
+        <v>132586357</v>
       </c>
       <c r="B48" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5918,13 +5918,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532410</v>
+        <v>532498</v>
       </c>
       <c r="R48" t="n">
-        <v>6921666</v>
+        <v>6921784</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5963,12 +5963,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>4 ex</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5995,32 +5990,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132586321</v>
+        <v>132586337</v>
       </c>
       <c r="B49" t="n">
-        <v>83163</v>
+        <v>99106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6030,13 +6025,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532447</v>
+        <v>532410</v>
       </c>
       <c r="R49" t="n">
-        <v>6921444</v>
+        <v>6921666</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6065,7 +6060,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6075,7 +6070,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6105,7 +6105,7 @@
         <v>132586329</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>132586346</v>
       </c>
       <c r="B51" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6321,32 +6321,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132586324</v>
+        <v>132586347</v>
       </c>
       <c r="B52" t="n">
-        <v>91892</v>
+        <v>80453</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532330</v>
+        <v>532521</v>
       </c>
       <c r="R52" t="n">
-        <v>6921453</v>
+        <v>6921732</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6428,32 +6428,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132586347</v>
+        <v>132586324</v>
       </c>
       <c r="B53" t="n">
-        <v>80451</v>
+        <v>91898</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532521</v>
+        <v>532330</v>
       </c>
       <c r="R53" t="n">
-        <v>6921732</v>
+        <v>6921453</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6535,32 +6535,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132586350</v>
+        <v>132586334</v>
       </c>
       <c r="B54" t="n">
-        <v>99098</v>
+        <v>80424</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6570,13 +6570,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532550</v>
+        <v>532417</v>
       </c>
       <c r="R54" t="n">
-        <v>6921717</v>
+        <v>6921637</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6615,12 +6615,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6647,32 +6642,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132586334</v>
+        <v>132586350</v>
       </c>
       <c r="B55" t="n">
-        <v>80422</v>
+        <v>99106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6682,13 +6677,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532417</v>
+        <v>532550</v>
       </c>
       <c r="R55" t="n">
-        <v>6921637</v>
+        <v>6921717</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6727,7 +6722,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6757,7 +6757,7 @@
         <v>132586328</v>
       </c>
       <c r="B56" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132586340</v>
+        <v>132586369</v>
       </c>
       <c r="B57" t="n">
-        <v>92191</v>
+        <v>57949</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6885,34 +6885,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532440</v>
+        <v>532097</v>
       </c>
       <c r="R57" t="n">
-        <v>6921699</v>
+        <v>6921643</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6944,7 +6952,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6954,7 +6962,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6981,10 +6994,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132586369</v>
+        <v>132586340</v>
       </c>
       <c r="B58" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6992,42 +7005,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532097</v>
+        <v>532440</v>
       </c>
       <c r="R58" t="n">
-        <v>6921643</v>
+        <v>6921699</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7059,7 +7064,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7069,12 +7074,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7104,7 +7104,7 @@
         <v>132586330</v>
       </c>
       <c r="B59" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132586315</v>
+        <v>132586375</v>
       </c>
       <c r="B60" t="n">
-        <v>92191</v>
+        <v>57949</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7219,34 +7219,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532561</v>
+        <v>532201</v>
       </c>
       <c r="R60" t="n">
-        <v>6921190</v>
+        <v>6921512</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7278,7 +7286,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7288,7 +7296,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7315,32 +7328,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132586325</v>
+        <v>132586315</v>
       </c>
       <c r="B61" t="n">
-        <v>5179</v>
+        <v>92197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7350,10 +7363,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532331</v>
+        <v>532561</v>
       </c>
       <c r="R61" t="n">
-        <v>6921451</v>
+        <v>6921190</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7385,7 +7398,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7395,7 +7408,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7422,53 +7435,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132586375</v>
+        <v>132586325</v>
       </c>
       <c r="B62" t="n">
-        <v>57948</v>
+        <v>5179</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>532201</v>
+        <v>532331</v>
       </c>
       <c r="R62" t="n">
-        <v>6921512</v>
+        <v>6921451</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7500,7 +7505,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7510,12 +7515,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7542,10 +7542,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132586373</v>
+        <v>132586377</v>
       </c>
       <c r="B63" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7577,13 +7577,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532239</v>
+        <v>532374</v>
       </c>
       <c r="R63" t="n">
-        <v>6921525</v>
+        <v>6921276</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7654,10 +7654,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132586377</v>
+        <v>132586373</v>
       </c>
       <c r="B64" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7689,13 +7689,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532374</v>
+        <v>532239</v>
       </c>
       <c r="R64" t="n">
-        <v>6921276</v>
+        <v>6921525</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7766,32 +7766,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132586333</v>
+        <v>132586356</v>
       </c>
       <c r="B65" t="n">
-        <v>91855</v>
+        <v>92358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7801,13 +7801,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532453</v>
+        <v>532498</v>
       </c>
       <c r="R65" t="n">
-        <v>6921617</v>
+        <v>6921779</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7873,10 +7873,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132586320</v>
+        <v>132586333</v>
       </c>
       <c r="B66" t="n">
-        <v>57136</v>
+        <v>91861</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7884,46 +7884,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532436</v>
+        <v>532453</v>
       </c>
       <c r="R66" t="n">
-        <v>6921359</v>
+        <v>6921617</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7955,7 +7943,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7965,7 +7953,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7995,7 +7983,7 @@
         <v>132586365</v>
       </c>
       <c r="B67" t="n">
-        <v>97211</v>
+        <v>97219</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,48 +8087,56 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132586356</v>
+        <v>132586366</v>
       </c>
       <c r="B68" t="n">
-        <v>92352</v>
+        <v>57949</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532498</v>
+        <v>532089</v>
       </c>
       <c r="R68" t="n">
-        <v>6921779</v>
+        <v>6921665</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8169,7 +8165,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8179,7 +8175,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8206,40 +8207,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132586366</v>
+        <v>132586320</v>
       </c>
       <c r="B69" t="n">
-        <v>57948</v>
+        <v>57137</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8249,10 +8254,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532089</v>
+        <v>532436</v>
       </c>
       <c r="R69" t="n">
-        <v>6921665</v>
+        <v>6921359</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8284,7 +8289,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8294,12 +8299,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -1417,53 +1417,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132586371</v>
+        <v>132586331</v>
       </c>
       <c r="B8" t="n">
-        <v>57949</v>
+        <v>99106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532200</v>
+        <v>532456</v>
       </c>
       <c r="R8" t="n">
-        <v>6921589</v>
+        <v>6921636</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1495,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1505,12 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,56 +1529,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132586359</v>
+        <v>132586342</v>
       </c>
       <c r="B9" t="n">
-        <v>57949</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532479</v>
+        <v>532450</v>
       </c>
       <c r="R9" t="n">
-        <v>6921806</v>
+        <v>6921712</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1625,12 +1609,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2085,45 +2069,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132586331</v>
+        <v>132586371</v>
       </c>
       <c r="B14" t="n">
-        <v>99106</v>
+        <v>57949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532456</v>
+        <v>532200</v>
       </c>
       <c r="R14" t="n">
-        <v>6921636</v>
+        <v>6921589</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2155,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2157,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,48 +2189,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132586342</v>
+        <v>132586359</v>
       </c>
       <c r="B15" t="n">
-        <v>99106</v>
+        <v>57949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532450</v>
+        <v>532479</v>
       </c>
       <c r="R15" t="n">
-        <v>6921712</v>
+        <v>6921806</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2640,32 +2640,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132586361</v>
+        <v>132586364</v>
       </c>
       <c r="B19" t="n">
-        <v>99106</v>
+        <v>97219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532468</v>
+        <v>532318</v>
       </c>
       <c r="R19" t="n">
-        <v>6921825</v>
+        <v>6921663</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,12 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,32 +2747,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132586364</v>
+        <v>132586361</v>
       </c>
       <c r="B20" t="n">
-        <v>97219</v>
+        <v>99106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,13 +2782,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532318</v>
+        <v>532468</v>
       </c>
       <c r="R20" t="n">
-        <v>6921663</v>
+        <v>6921825</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2822,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2827,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3095,56 +3095,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132586367</v>
+        <v>132586354</v>
       </c>
       <c r="B23" t="n">
-        <v>57949</v>
+        <v>80453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532091</v>
+        <v>532535</v>
       </c>
       <c r="R23" t="n">
-        <v>6921651</v>
+        <v>6921758</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3173,7 +3165,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3183,12 +3175,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3215,32 +3202,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132586354</v>
+        <v>132586355</v>
       </c>
       <c r="B24" t="n">
-        <v>80453</v>
+        <v>79319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3250,13 +3237,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532535</v>
+        <v>532518</v>
       </c>
       <c r="R24" t="n">
-        <v>6921758</v>
+        <v>6921775</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3285,7 +3272,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,7 +3282,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,10 +3309,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132586355</v>
+        <v>132586367</v>
       </c>
       <c r="B25" t="n">
-        <v>79319</v>
+        <v>57949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3333,37 +3320,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532518</v>
+        <v>532091</v>
       </c>
       <c r="R25" t="n">
-        <v>6921775</v>
+        <v>6921651</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3392,7 +3387,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3402,7 +3397,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -1417,45 +1417,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132586331</v>
+        <v>132586371</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532456</v>
+        <v>532200</v>
       </c>
       <c r="R8" t="n">
-        <v>6921636</v>
+        <v>6921589</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1487,7 +1495,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1505,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,48 +1537,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132586342</v>
+        <v>132586359</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532450</v>
+        <v>532479</v>
       </c>
       <c r="R9" t="n">
-        <v>6921712</v>
+        <v>6921806</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,7 +1615,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,12 +1625,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,7 +1660,7 @@
         <v>132586322</v>
       </c>
       <c r="B10" t="n">
-        <v>97219</v>
+        <v>97229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1767,7 @@
         <v>132586358</v>
       </c>
       <c r="B11" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1874,7 @@
         <v>132586345</v>
       </c>
       <c r="B12" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1981,7 @@
         <v>132586319</v>
       </c>
       <c r="B13" t="n">
-        <v>80452</v>
+        <v>80460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,53 +2085,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132586371</v>
+        <v>132586331</v>
       </c>
       <c r="B14" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532200</v>
+        <v>532456</v>
       </c>
       <c r="R14" t="n">
-        <v>6921589</v>
+        <v>6921636</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2147,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,12 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,56 +2197,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132586359</v>
+        <v>132586342</v>
       </c>
       <c r="B15" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532479</v>
+        <v>532450</v>
       </c>
       <c r="R15" t="n">
-        <v>6921806</v>
+        <v>6921712</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2312,7 @@
         <v>132586317</v>
       </c>
       <c r="B16" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>132586335</v>
       </c>
       <c r="B17" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>132586323</v>
       </c>
       <c r="B18" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,48 +2640,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132586364</v>
+        <v>132586336</v>
       </c>
       <c r="B19" t="n">
-        <v>97219</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532318</v>
+        <v>532410</v>
       </c>
       <c r="R19" t="n">
-        <v>6921663</v>
+        <v>6921645</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2732,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Kunde inte se med kikaren om det var både en hane och en hona. Men den ena födosökte uteslutande högt upp i träden, medan den andra var lågt ner på flera stammar. Möjligen utifrån detta att det handlar om en hane och en hona.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,32 +2764,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132586361</v>
+        <v>132586364</v>
       </c>
       <c r="B20" t="n">
-        <v>99106</v>
+        <v>97229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,13 +2799,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532468</v>
+        <v>532318</v>
       </c>
       <c r="R20" t="n">
-        <v>6921825</v>
+        <v>6921663</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2817,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,12 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,60 +2871,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132586336</v>
+        <v>132586361</v>
       </c>
       <c r="B21" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532410</v>
+        <v>532468</v>
       </c>
       <c r="R21" t="n">
-        <v>6921645</v>
+        <v>6921825</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Kunde inte se med kikaren om det var både en hane och en hona. Men den ena födosökte uteslutande högt upp i träden, medan den andra var lågt ner på flera stammar. Möjligen utifrån detta att det handlar om en hane och en hona.</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,7 +2986,7 @@
         <v>132586344</v>
       </c>
       <c r="B22" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>132586354</v>
       </c>
       <c r="B23" t="n">
-        <v>80453</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>132586355</v>
       </c>
       <c r="B24" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>132586367</v>
       </c>
       <c r="B25" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>132586332</v>
       </c>
       <c r="B26" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>132586314</v>
       </c>
       <c r="B27" t="n">
-        <v>92322</v>
+        <v>92332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3656,60 +3656,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132586349</v>
+        <v>132586326</v>
       </c>
       <c r="B28" t="n">
-        <v>58110</v>
+        <v>99116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532533</v>
+        <v>532327</v>
       </c>
       <c r="R28" t="n">
-        <v>6921722</v>
+        <v>6921455</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3738,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3748,7 +3736,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>140 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3778,7 +3771,7 @@
         <v>132586351</v>
       </c>
       <c r="B29" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,10 +3875,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132586316</v>
+        <v>132586338</v>
       </c>
       <c r="B30" t="n">
-        <v>79319</v>
+        <v>92207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3893,21 +3886,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3917,13 +3910,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532580</v>
+        <v>532424</v>
       </c>
       <c r="R30" t="n">
-        <v>6921193</v>
+        <v>6921684</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3952,7 +3945,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3962,7 +3955,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,10 +3982,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132586338</v>
+        <v>132586316</v>
       </c>
       <c r="B31" t="n">
-        <v>92197</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4000,21 +3993,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4024,13 +4017,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532424</v>
+        <v>532580</v>
       </c>
       <c r="R31" t="n">
-        <v>6921684</v>
+        <v>6921193</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4059,7 +4052,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4069,7 +4062,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4099,7 +4092,7 @@
         <v>132586348</v>
       </c>
       <c r="B32" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4203,48 +4196,60 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132586326</v>
+        <v>132586349</v>
       </c>
       <c r="B33" t="n">
-        <v>99106</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>532327</v>
+        <v>532533</v>
       </c>
       <c r="R33" t="n">
-        <v>6921455</v>
+        <v>6921722</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4273,7 +4278,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4283,12 +4288,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>140 ex</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4318,7 +4318,7 @@
         <v>132586352</v>
       </c>
       <c r="B34" t="n">
-        <v>92322</v>
+        <v>92332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4422,10 +4422,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132586343</v>
+        <v>132586370</v>
       </c>
       <c r="B35" t="n">
-        <v>83165</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,37 +4433,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>532452</v>
+        <v>532196</v>
       </c>
       <c r="R35" t="n">
-        <v>6921716</v>
+        <v>6921594</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4492,7 +4500,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4502,7 +4510,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4529,10 +4542,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132586370</v>
+        <v>132586368</v>
       </c>
       <c r="B36" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4572,10 +4585,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532196</v>
+        <v>532092</v>
       </c>
       <c r="R36" t="n">
-        <v>6921594</v>
+        <v>6921646</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4607,7 +4620,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4617,12 +4630,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4662,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132586368</v>
+        <v>132586343</v>
       </c>
       <c r="B37" t="n">
-        <v>57949</v>
+        <v>83173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,45 +4673,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532092</v>
+        <v>532452</v>
       </c>
       <c r="R37" t="n">
-        <v>6921646</v>
+        <v>6921716</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4727,7 +4732,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,12 +4742,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4772,7 +4772,7 @@
         <v>132586341</v>
       </c>
       <c r="B38" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>132586372</v>
       </c>
       <c r="B39" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>132586374</v>
       </c>
       <c r="B40" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132586313</v>
+        <v>132586339</v>
       </c>
       <c r="B41" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532576</v>
+        <v>532433</v>
       </c>
       <c r="R41" t="n">
-        <v>6921203</v>
+        <v>6921682</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5196,12 +5196,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5231,7 +5226,7 @@
         <v>132586353</v>
       </c>
       <c r="B42" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,7 +5333,7 @@
         <v>132586318</v>
       </c>
       <c r="B43" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5442,10 +5437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132586339</v>
+        <v>132586313</v>
       </c>
       <c r="B44" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5453,21 +5448,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5477,13 +5472,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532433</v>
+        <v>532576</v>
       </c>
       <c r="R44" t="n">
-        <v>6921682</v>
+        <v>6921203</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5512,7 +5507,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5522,7 +5517,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5552,7 +5552,7 @@
         <v>132586363</v>
       </c>
       <c r="B45" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>132586360</v>
       </c>
       <c r="B46" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5776,32 +5776,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132586321</v>
+        <v>132586337</v>
       </c>
       <c r="B47" t="n">
-        <v>83165</v>
+        <v>99116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5811,13 +5811,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532447</v>
+        <v>532410</v>
       </c>
       <c r="R47" t="n">
-        <v>6921444</v>
+        <v>6921666</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5856,7 +5856,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5883,32 +5888,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132586357</v>
+        <v>132586329</v>
       </c>
       <c r="B48" t="n">
-        <v>91898</v>
+        <v>99116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5918,10 +5923,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532498</v>
+        <v>532354</v>
       </c>
       <c r="R48" t="n">
-        <v>6921784</v>
+        <v>6921519</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5953,7 +5958,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5963,7 +5968,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5990,32 +6000,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132586337</v>
+        <v>132586321</v>
       </c>
       <c r="B49" t="n">
-        <v>99106</v>
+        <v>83173</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6025,13 +6035,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532410</v>
+        <v>532447</v>
       </c>
       <c r="R49" t="n">
-        <v>6921666</v>
+        <v>6921444</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6060,7 +6070,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6070,12 +6080,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>4 ex</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6102,32 +6107,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132586329</v>
+        <v>132586357</v>
       </c>
       <c r="B50" t="n">
-        <v>99106</v>
+        <v>91908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6137,10 +6142,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532354</v>
+        <v>532498</v>
       </c>
       <c r="R50" t="n">
-        <v>6921519</v>
+        <v>6921784</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6172,7 +6177,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6182,12 +6187,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6217,7 +6217,7 @@
         <v>132586346</v>
       </c>
       <c r="B51" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>132586347</v>
       </c>
       <c r="B52" t="n">
-        <v>80453</v>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>132586324</v>
       </c>
       <c r="B53" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>132586334</v>
       </c>
       <c r="B54" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>132586350</v>
       </c>
       <c r="B55" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>132586328</v>
       </c>
       <c r="B56" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>132586369</v>
       </c>
       <c r="B57" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>132586340</v>
       </c>
       <c r="B58" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>132586330</v>
       </c>
       <c r="B59" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132586375</v>
+        <v>132586315</v>
       </c>
       <c r="B60" t="n">
-        <v>57949</v>
+        <v>92207</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7219,42 +7219,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532201</v>
+        <v>532561</v>
       </c>
       <c r="R60" t="n">
-        <v>6921512</v>
+        <v>6921190</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7286,7 +7278,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7296,12 +7288,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7328,32 +7315,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132586315</v>
+        <v>132586325</v>
       </c>
       <c r="B61" t="n">
-        <v>92197</v>
+        <v>5179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7363,10 +7350,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532561</v>
+        <v>532331</v>
       </c>
       <c r="R61" t="n">
-        <v>6921190</v>
+        <v>6921451</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7398,7 +7385,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7408,7 +7395,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7435,45 +7422,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132586325</v>
+        <v>132586375</v>
       </c>
       <c r="B62" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>532331</v>
+        <v>532201</v>
       </c>
       <c r="R62" t="n">
-        <v>6921451</v>
+        <v>6921512</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7505,7 +7500,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7515,7 +7510,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7545,7 +7545,7 @@
         <v>132586377</v>
       </c>
       <c r="B63" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>132586373</v>
       </c>
       <c r="B64" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132586356</v>
+        <v>132586333</v>
       </c>
       <c r="B65" t="n">
-        <v>92358</v>
+        <v>91871</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7801,13 +7801,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532498</v>
+        <v>532453</v>
       </c>
       <c r="R65" t="n">
-        <v>6921779</v>
+        <v>6921617</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7873,10 +7873,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132586333</v>
+        <v>132586365</v>
       </c>
       <c r="B66" t="n">
-        <v>91861</v>
+        <v>97229</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7884,21 +7884,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7908,13 +7908,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532453</v>
+        <v>532184</v>
       </c>
       <c r="R66" t="n">
-        <v>6921617</v>
+        <v>6921738</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132586365</v>
+        <v>132586356</v>
       </c>
       <c r="B67" t="n">
-        <v>97219</v>
+        <v>92368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532184</v>
+        <v>532498</v>
       </c>
       <c r="R67" t="n">
-        <v>6921738</v>
+        <v>6921779</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8087,40 +8087,44 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132586366</v>
+        <v>132586320</v>
       </c>
       <c r="B68" t="n">
-        <v>57949</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8130,10 +8134,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532089</v>
+        <v>532436</v>
       </c>
       <c r="R68" t="n">
-        <v>6921665</v>
+        <v>6921359</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8165,7 +8169,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8175,12 +8179,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8207,44 +8206,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132586320</v>
+        <v>132586366</v>
       </c>
       <c r="B69" t="n">
-        <v>57137</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8254,10 +8249,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532436</v>
+        <v>532089</v>
       </c>
       <c r="R69" t="n">
-        <v>6921359</v>
+        <v>6921665</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8289,7 +8284,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8299,7 +8294,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -1417,53 +1417,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132586371</v>
+        <v>132586322</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>97230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532200</v>
+        <v>532371</v>
       </c>
       <c r="R8" t="n">
-        <v>6921589</v>
+        <v>6921471</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1495,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1505,12 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132586359</v>
+        <v>132586358</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,45 +1535,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532479</v>
+        <v>532488</v>
       </c>
       <c r="R9" t="n">
-        <v>6921806</v>
+        <v>6921801</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1625,12 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,32 +1631,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132586322</v>
+        <v>132586345</v>
       </c>
       <c r="B10" t="n">
-        <v>97229</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1692,13 +1666,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532371</v>
+        <v>532451</v>
       </c>
       <c r="R10" t="n">
-        <v>6921471</v>
+        <v>6921744</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1737,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,32 +1738,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132586358</v>
+        <v>132586319</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>80460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532488</v>
+        <v>532428</v>
       </c>
       <c r="R11" t="n">
-        <v>6921801</v>
+        <v>6921348</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132586345</v>
+        <v>132586359</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,37 +1856,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532451</v>
+        <v>532479</v>
       </c>
       <c r="R12" t="n">
-        <v>6921744</v>
+        <v>6921806</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1941,7 +1923,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,7 +1933,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,48 +1965,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132586319</v>
+        <v>132586371</v>
       </c>
       <c r="B13" t="n">
-        <v>80460</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532428</v>
+        <v>532200</v>
       </c>
       <c r="R13" t="n">
-        <v>6921348</v>
+        <v>6921589</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2048,7 +2043,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2053,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,7 +2088,7 @@
         <v>132586331</v>
       </c>
       <c r="B14" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132586342</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132586317</v>
       </c>
       <c r="B16" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>132586335</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>132586323</v>
       </c>
       <c r="B18" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,60 +2640,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132586336</v>
+        <v>132586361</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>99117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532410</v>
+        <v>532468</v>
       </c>
       <c r="R19" t="n">
-        <v>6921645</v>
+        <v>6921825</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2722,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2732,12 +2720,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Kunde inte se med kikaren om det var både en hane och en hona. Men den ena födosökte uteslutande högt upp i träden, medan den andra var lågt ner på flera stammar. Möjligen utifrån detta att det handlar om en hane och en hona.</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,7 +2755,7 @@
         <v>132586364</v>
       </c>
       <c r="B20" t="n">
-        <v>97229</v>
+        <v>97230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,48 +2859,60 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132586361</v>
+        <v>132586336</v>
       </c>
       <c r="B21" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532468</v>
+        <v>532410</v>
       </c>
       <c r="R21" t="n">
-        <v>6921825</v>
+        <v>6921645</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Kunde inte se med kikaren om det var både en hane och en hona. Men den ena födosökte uteslutande högt upp i träden, medan den andra var lågt ner på flera stammar. Möjligen utifrån detta att det handlar om en hane och en hona.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,7 +2986,7 @@
         <v>132586344</v>
       </c>
       <c r="B22" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>132586314</v>
       </c>
       <c r="B27" t="n">
-        <v>92332</v>
+        <v>92333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3656,32 +3656,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132586326</v>
+        <v>132586351</v>
       </c>
       <c r="B28" t="n">
-        <v>99116</v>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3691,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532327</v>
+        <v>532556</v>
       </c>
       <c r="R28" t="n">
-        <v>6921455</v>
+        <v>6921736</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,12 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>140 ex</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132586351</v>
+        <v>132586338</v>
       </c>
       <c r="B29" t="n">
-        <v>83173</v>
+        <v>92208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3779,21 +3774,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3803,13 +3798,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>532556</v>
+        <v>532424</v>
       </c>
       <c r="R29" t="n">
-        <v>6921736</v>
+        <v>6921684</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3838,7 +3833,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3843,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,10 +3870,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132586338</v>
+        <v>132586316</v>
       </c>
       <c r="B30" t="n">
-        <v>92207</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3886,21 +3881,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3910,13 +3905,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532424</v>
+        <v>532580</v>
       </c>
       <c r="R30" t="n">
-        <v>6921684</v>
+        <v>6921193</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3945,7 +3940,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3955,7 +3950,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,10 +3977,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132586316</v>
+        <v>132586348</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3993,21 +3988,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,13 +4012,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532580</v>
+        <v>532526</v>
       </c>
       <c r="R31" t="n">
-        <v>6921193</v>
+        <v>6921737</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4052,7 +4047,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4062,7 +4057,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,32 +4084,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132586348</v>
+        <v>132586326</v>
       </c>
       <c r="B32" t="n">
-        <v>80432</v>
+        <v>99117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4124,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532526</v>
+        <v>532327</v>
       </c>
       <c r="R32" t="n">
-        <v>6921737</v>
+        <v>6921455</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4159,7 +4154,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4169,7 +4164,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>140 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,48 +4315,56 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132586352</v>
+        <v>132586368</v>
       </c>
       <c r="B34" t="n">
-        <v>92332</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>532543</v>
+        <v>532092</v>
       </c>
       <c r="R34" t="n">
-        <v>6921755</v>
+        <v>6921646</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4385,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4395,7 +4403,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4542,56 +4555,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132586368</v>
+        <v>132586352</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>92333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532092</v>
+        <v>532543</v>
       </c>
       <c r="R36" t="n">
-        <v>6921646</v>
+        <v>6921755</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4620,7 +4625,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4630,12 +4635,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4772,7 +4772,7 @@
         <v>132586341</v>
       </c>
       <c r="B38" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>132586339</v>
       </c>
       <c r="B41" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>132586363</v>
       </c>
       <c r="B45" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5776,32 +5776,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132586337</v>
+        <v>132586321</v>
       </c>
       <c r="B47" t="n">
-        <v>99116</v>
+        <v>83173</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5811,13 +5811,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532410</v>
+        <v>532447</v>
       </c>
       <c r="R47" t="n">
-        <v>6921666</v>
+        <v>6921444</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5856,12 +5856,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4 ex</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5888,32 +5883,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132586329</v>
+        <v>132586357</v>
       </c>
       <c r="B48" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5923,10 +5918,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532354</v>
+        <v>532498</v>
       </c>
       <c r="R48" t="n">
-        <v>6921519</v>
+        <v>6921784</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5958,7 +5953,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5968,12 +5963,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6000,32 +5990,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132586321</v>
+        <v>132586337</v>
       </c>
       <c r="B49" t="n">
-        <v>83173</v>
+        <v>99117</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6035,13 +6025,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532447</v>
+        <v>532410</v>
       </c>
       <c r="R49" t="n">
-        <v>6921444</v>
+        <v>6921666</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6070,7 +6060,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6080,7 +6070,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6107,32 +6102,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132586357</v>
+        <v>132586329</v>
       </c>
       <c r="B50" t="n">
-        <v>91908</v>
+        <v>99117</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6142,10 +6137,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532498</v>
+        <v>532354</v>
       </c>
       <c r="R50" t="n">
-        <v>6921784</v>
+        <v>6921519</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6177,7 +6172,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6187,7 +6182,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6214,10 +6214,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132586346</v>
+        <v>132586324</v>
       </c>
       <c r="B51" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532520</v>
+        <v>532330</v>
       </c>
       <c r="R51" t="n">
-        <v>6921725</v>
+        <v>6921453</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132586347</v>
+        <v>132586346</v>
       </c>
       <c r="B52" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,13 +6356,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532521</v>
+        <v>532520</v>
       </c>
       <c r="R52" t="n">
-        <v>6921732</v>
+        <v>6921725</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6428,32 +6428,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132586324</v>
+        <v>132586347</v>
       </c>
       <c r="B53" t="n">
-        <v>91908</v>
+        <v>80461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532330</v>
+        <v>532521</v>
       </c>
       <c r="R53" t="n">
-        <v>6921453</v>
+        <v>6921732</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6645,7 +6645,7 @@
         <v>132586350</v>
       </c>
       <c r="B55" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6754,10 +6754,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132586328</v>
+        <v>132586340</v>
       </c>
       <c r="B56" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6765,45 +6765,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532350</v>
+        <v>532440</v>
       </c>
       <c r="R56" t="n">
-        <v>6921513</v>
+        <v>6921699</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6832,7 +6824,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6842,12 +6834,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6874,53 +6861,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132586369</v>
+        <v>132586330</v>
       </c>
       <c r="B57" t="n">
-        <v>57953</v>
+        <v>80336</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532097</v>
+        <v>532342</v>
       </c>
       <c r="R57" t="n">
-        <v>6921643</v>
+        <v>6921556</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6952,7 +6931,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6962,12 +6941,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6994,10 +6968,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132586340</v>
+        <v>132586328</v>
       </c>
       <c r="B58" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7005,37 +6979,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532440</v>
+        <v>532350</v>
       </c>
       <c r="R58" t="n">
-        <v>6921699</v>
+        <v>6921513</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7064,7 +7046,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7074,7 +7056,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7101,45 +7088,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132586330</v>
+        <v>132586369</v>
       </c>
       <c r="B59" t="n">
-        <v>80336</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532342</v>
+        <v>532097</v>
       </c>
       <c r="R59" t="n">
-        <v>6921556</v>
+        <v>6921643</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7171,7 +7166,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7181,7 +7176,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7211,7 +7211,7 @@
         <v>132586315</v>
       </c>
       <c r="B60" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7315,45 +7315,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132586325</v>
+        <v>132586375</v>
       </c>
       <c r="B61" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532331</v>
+        <v>532201</v>
       </c>
       <c r="R61" t="n">
-        <v>6921451</v>
+        <v>6921512</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7385,7 +7393,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7395,7 +7403,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7422,53 +7435,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132586375</v>
+        <v>132586325</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>5179</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>532201</v>
+        <v>532331</v>
       </c>
       <c r="R62" t="n">
-        <v>6921512</v>
+        <v>6921451</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7500,7 +7505,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7510,12 +7515,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7545,7 +7545,7 @@
         <v>132586377</v>
       </c>
       <c r="B63" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>132586373</v>
       </c>
       <c r="B64" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132586333</v>
+        <v>132586356</v>
       </c>
       <c r="B65" t="n">
-        <v>91871</v>
+        <v>92369</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7801,13 +7801,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532453</v>
+        <v>532498</v>
       </c>
       <c r="R65" t="n">
-        <v>6921617</v>
+        <v>6921779</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7876,7 +7876,7 @@
         <v>132586365</v>
       </c>
       <c r="B66" t="n">
-        <v>97229</v>
+        <v>97230</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132586356</v>
+        <v>132586333</v>
       </c>
       <c r="B67" t="n">
-        <v>92368</v>
+        <v>91872</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532498</v>
+        <v>532453</v>
       </c>
       <c r="R67" t="n">
-        <v>6921779</v>
+        <v>6921617</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -1524,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132586358</v>
+        <v>132586371</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,37 +1535,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532488</v>
+        <v>532200</v>
       </c>
       <c r="R9" t="n">
-        <v>6921801</v>
+        <v>6921589</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1612,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132586345</v>
+        <v>132586359</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,37 +1655,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532451</v>
+        <v>532479</v>
       </c>
       <c r="R10" t="n">
-        <v>6921744</v>
+        <v>6921806</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1732,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,32 +1764,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132586319</v>
+        <v>132586331</v>
       </c>
       <c r="B11" t="n">
-        <v>80466</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,13 +1799,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532428</v>
+        <v>532456</v>
       </c>
       <c r="R11" t="n">
-        <v>6921348</v>
+        <v>6921636</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1834,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1844,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,7 +1876,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132586331</v>
+        <v>132586342</v>
       </c>
       <c r="B12" t="n">
         <v>99130</v>
@@ -1880,13 +1911,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532456</v>
+        <v>532450</v>
       </c>
       <c r="R12" t="n">
-        <v>6921636</v>
+        <v>6921712</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,12 +1956,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,32 +1988,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132586342</v>
+        <v>132586358</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532450</v>
+        <v>532488</v>
       </c>
       <c r="R13" t="n">
-        <v>6921712</v>
+        <v>6921801</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,12 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>30 ex</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132586359</v>
+        <v>132586345</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,45 +2106,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532479</v>
+        <v>532451</v>
       </c>
       <c r="R14" t="n">
-        <v>6921806</v>
+        <v>6921744</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2147,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,12 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,56 +2202,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132586371</v>
+        <v>132586319</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>80466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532200</v>
+        <v>532428</v>
       </c>
       <c r="R15" t="n">
-        <v>6921589</v>
+        <v>6921348</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,7 +2272,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,12 +2282,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,32 +2309,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132586317</v>
+        <v>132586335</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532572</v>
+        <v>532420</v>
       </c>
       <c r="R16" t="n">
-        <v>6921218</v>
+        <v>6921638</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2389,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,7 +2421,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132586335</v>
+        <v>132586323</v>
       </c>
       <c r="B17" t="n">
         <v>99130</v>
@@ -2451,10 +2456,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532420</v>
+        <v>532346</v>
       </c>
       <c r="R17" t="n">
-        <v>6921638</v>
+        <v>6921473</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2486,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,12 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,32 +2533,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132586323</v>
+        <v>132586317</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2563,13 +2568,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532346</v>
+        <v>532572</v>
       </c>
       <c r="R18" t="n">
-        <v>6921473</v>
+        <v>6921218</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,12 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132586351</v>
+        <v>132586316</v>
       </c>
       <c r="B28" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3691,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532556</v>
+        <v>532580</v>
       </c>
       <c r="R28" t="n">
-        <v>6921736</v>
+        <v>6921193</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,10 +3763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132586338</v>
+        <v>132586349</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>58119</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,37 +3774,49 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>532424</v>
+        <v>532533</v>
       </c>
       <c r="R29" t="n">
-        <v>6921684</v>
+        <v>6921722</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3833,7 +3845,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3843,7 +3855,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,10 +3882,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132586316</v>
+        <v>132586351</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3881,21 +3893,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3905,13 +3917,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532580</v>
+        <v>532556</v>
       </c>
       <c r="R30" t="n">
-        <v>6921193</v>
+        <v>6921736</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3940,7 +3952,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3950,7 +3962,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3977,10 +3989,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132586348</v>
+        <v>132586338</v>
       </c>
       <c r="B31" t="n">
-        <v>80438</v>
+        <v>92217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,21 +4000,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4012,10 +4024,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532526</v>
+        <v>532424</v>
       </c>
       <c r="R31" t="n">
-        <v>6921737</v>
+        <v>6921684</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4047,7 +4059,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4057,7 +4069,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,10 +4096,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132586349</v>
+        <v>132586348</v>
       </c>
       <c r="B32" t="n">
-        <v>58119</v>
+        <v>80438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4095,49 +4107,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532533</v>
+        <v>532526</v>
       </c>
       <c r="R32" t="n">
-        <v>6921722</v>
+        <v>6921737</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,7 +4315,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132586368</v>
+        <v>132586370</v>
       </c>
       <c r="B34" t="n">
         <v>57958</v>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>532092</v>
+        <v>532196</v>
       </c>
       <c r="R34" t="n">
-        <v>6921646</v>
+        <v>6921594</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,7 +4435,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132586370</v>
+        <v>132586368</v>
       </c>
       <c r="B35" t="n">
         <v>57958</v>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>532196</v>
+        <v>532092</v>
       </c>
       <c r="R35" t="n">
-        <v>6921594</v>
+        <v>6921646</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4555,32 +4555,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132586352</v>
+        <v>132586343</v>
       </c>
       <c r="B36" t="n">
-        <v>92342</v>
+        <v>83181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532543</v>
+        <v>532452</v>
       </c>
       <c r="R36" t="n">
-        <v>6921755</v>
+        <v>6921716</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,32 +4662,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132586343</v>
+        <v>132586352</v>
       </c>
       <c r="B37" t="n">
-        <v>83181</v>
+        <v>92342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>4217</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532452</v>
+        <v>532543</v>
       </c>
       <c r="R37" t="n">
-        <v>6921716</v>
+        <v>6921755</v>
       </c>
       <c r="S37" t="n">
         <v>6</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132586353</v>
+        <v>132586339</v>
       </c>
       <c r="B41" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532536</v>
+        <v>532433</v>
       </c>
       <c r="R41" t="n">
-        <v>6921758</v>
+        <v>6921682</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5223,10 +5223,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132586318</v>
+        <v>132586353</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5258,13 +5258,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532537</v>
+        <v>532536</v>
       </c>
       <c r="R42" t="n">
-        <v>6921239</v>
+        <v>6921758</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,10 +5330,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132586339</v>
+        <v>132586318</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5341,21 +5341,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,13 +5365,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>532433</v>
+        <v>532537</v>
       </c>
       <c r="R43" t="n">
-        <v>6921682</v>
+        <v>6921239</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5776,32 +5776,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132586321</v>
+        <v>132586329</v>
       </c>
       <c r="B47" t="n">
-        <v>83181</v>
+        <v>99130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5811,13 +5811,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532447</v>
+        <v>532354</v>
       </c>
       <c r="R47" t="n">
-        <v>6921444</v>
+        <v>6921519</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5856,7 +5856,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5883,32 +5888,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132586357</v>
+        <v>132586337</v>
       </c>
       <c r="B48" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5918,13 +5923,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532498</v>
+        <v>532410</v>
       </c>
       <c r="R48" t="n">
-        <v>6921784</v>
+        <v>6921666</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5953,7 +5958,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5963,7 +5968,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5990,32 +6000,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132586329</v>
+        <v>132586321</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>83181</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6025,13 +6035,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532354</v>
+        <v>532447</v>
       </c>
       <c r="R49" t="n">
-        <v>6921519</v>
+        <v>6921444</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6060,7 +6070,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6070,12 +6080,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6102,32 +6107,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132586337</v>
+        <v>132586357</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6137,13 +6142,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532410</v>
+        <v>532498</v>
       </c>
       <c r="R50" t="n">
-        <v>6921666</v>
+        <v>6921784</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6172,7 +6177,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6182,12 +6187,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>4 ex</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6214,10 +6214,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132586324</v>
+        <v>132586346</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532330</v>
+        <v>532520</v>
       </c>
       <c r="R51" t="n">
-        <v>6921453</v>
+        <v>6921725</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132586346</v>
+        <v>132586347</v>
       </c>
       <c r="B52" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,13 +6356,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532520</v>
+        <v>532521</v>
       </c>
       <c r="R52" t="n">
-        <v>6921725</v>
+        <v>6921732</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6428,32 +6428,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132586347</v>
+        <v>132586324</v>
       </c>
       <c r="B53" t="n">
-        <v>80467</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532521</v>
+        <v>532330</v>
       </c>
       <c r="R53" t="n">
-        <v>6921732</v>
+        <v>6921453</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6535,32 +6535,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132586350</v>
+        <v>132586334</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6570,13 +6570,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532550</v>
+        <v>532417</v>
       </c>
       <c r="R54" t="n">
-        <v>6921717</v>
+        <v>6921637</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6615,12 +6615,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6647,32 +6642,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132586334</v>
+        <v>132586350</v>
       </c>
       <c r="B55" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6682,13 +6677,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532417</v>
+        <v>532550</v>
       </c>
       <c r="R55" t="n">
-        <v>6921637</v>
+        <v>6921717</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6727,7 +6722,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7766,60 +7766,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132586320</v>
+        <v>132586356</v>
       </c>
       <c r="B65" t="n">
-        <v>57145</v>
+        <v>92378</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532436</v>
+        <v>532498</v>
       </c>
       <c r="R65" t="n">
-        <v>6921359</v>
+        <v>6921779</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7848,7 +7836,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7858,7 +7846,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7885,32 +7873,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132586356</v>
+        <v>132586333</v>
       </c>
       <c r="B66" t="n">
-        <v>92378</v>
+        <v>91881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7920,13 +7908,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532498</v>
+        <v>532453</v>
       </c>
       <c r="R66" t="n">
-        <v>6921779</v>
+        <v>6921617</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7955,7 +7943,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7965,7 +7953,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7992,48 +7980,56 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132586365</v>
+        <v>132586366</v>
       </c>
       <c r="B67" t="n">
-        <v>97243</v>
+        <v>57958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532184</v>
+        <v>532089</v>
       </c>
       <c r="R67" t="n">
-        <v>6921738</v>
+        <v>6921665</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8062,7 +8058,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8072,7 +8068,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8099,10 +8100,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132586333</v>
+        <v>132586365</v>
       </c>
       <c r="B68" t="n">
-        <v>91881</v>
+        <v>97243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8110,21 +8111,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8134,13 +8135,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532453</v>
+        <v>532184</v>
       </c>
       <c r="R68" t="n">
-        <v>6921617</v>
+        <v>6921738</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8169,7 +8170,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8179,7 +8180,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8206,40 +8207,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132586366</v>
+        <v>132586320</v>
       </c>
       <c r="B69" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8249,10 +8254,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532089</v>
+        <v>532436</v>
       </c>
       <c r="R69" t="n">
-        <v>6921665</v>
+        <v>6921359</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8284,7 +8289,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8294,12 +8299,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -1417,32 +1417,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132586322</v>
+        <v>132586331</v>
       </c>
       <c r="B8" t="n">
-        <v>97243</v>
+        <v>99130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532371</v>
+        <v>532456</v>
       </c>
       <c r="R8" t="n">
-        <v>6921471</v>
+        <v>6921636</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,56 +1529,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132586371</v>
+        <v>132586342</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532200</v>
+        <v>532450</v>
       </c>
       <c r="R9" t="n">
-        <v>6921589</v>
+        <v>6921712</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,12 +1609,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,53 +1641,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132586359</v>
+        <v>132586322</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>97243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532479</v>
+        <v>532371</v>
       </c>
       <c r="R10" t="n">
-        <v>6921806</v>
+        <v>6921471</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1722,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,12 +1721,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,32 +1748,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132586331</v>
+        <v>132586358</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1799,13 +1783,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532456</v>
+        <v>532488</v>
       </c>
       <c r="R11" t="n">
-        <v>6921636</v>
+        <v>6921801</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,12 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,32 +1855,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132586342</v>
+        <v>132586345</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,13 +1890,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532450</v>
+        <v>532451</v>
       </c>
       <c r="R12" t="n">
-        <v>6921712</v>
+        <v>6921744</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,12 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>30 ex</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,32 +1962,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132586358</v>
+        <v>132586319</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>80466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,13 +1997,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532488</v>
+        <v>532428</v>
       </c>
       <c r="R13" t="n">
-        <v>6921801</v>
+        <v>6921348</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2058,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132586345</v>
+        <v>132586371</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,37 +2080,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532451</v>
+        <v>532200</v>
       </c>
       <c r="R14" t="n">
-        <v>6921744</v>
+        <v>6921589</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2157,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,48 +2189,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132586319</v>
+        <v>132586359</v>
       </c>
       <c r="B15" t="n">
-        <v>80466</v>
+        <v>57958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532428</v>
+        <v>532479</v>
       </c>
       <c r="R15" t="n">
-        <v>6921348</v>
+        <v>6921806</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,32 +2309,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132586335</v>
+        <v>132586317</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532420</v>
+        <v>532572</v>
       </c>
       <c r="R16" t="n">
-        <v>6921638</v>
+        <v>6921218</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,12 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,7 +2416,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132586323</v>
+        <v>132586335</v>
       </c>
       <c r="B17" t="n">
         <v>99130</v>
@@ -2456,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532346</v>
+        <v>532420</v>
       </c>
       <c r="R17" t="n">
-        <v>6921473</v>
+        <v>6921638</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2491,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,12 +2496,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,32 +2528,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132586317</v>
+        <v>132586323</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2568,13 +2563,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532572</v>
+        <v>532346</v>
       </c>
       <c r="R18" t="n">
-        <v>6921218</v>
+        <v>6921473</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2608,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,32 +2640,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132586364</v>
+        <v>132586361</v>
       </c>
       <c r="B19" t="n">
-        <v>97243</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532318</v>
+        <v>532468</v>
       </c>
       <c r="R19" t="n">
-        <v>6921663</v>
+        <v>6921825</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2871,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132586361</v>
+        <v>132586364</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>97243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,13 +2911,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532468</v>
+        <v>532318</v>
       </c>
       <c r="R21" t="n">
-        <v>6921825</v>
+        <v>6921663</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2951,12 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>5 ex</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,48 +3095,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132586354</v>
+        <v>132586367</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532535</v>
+        <v>532091</v>
       </c>
       <c r="R23" t="n">
-        <v>6921758</v>
+        <v>6921651</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3165,7 +3173,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3183,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,32 +3215,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132586355</v>
+        <v>132586354</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3237,13 +3250,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532518</v>
+        <v>532535</v>
       </c>
       <c r="R24" t="n">
-        <v>6921775</v>
+        <v>6921758</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3272,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3295,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,10 +3322,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132586367</v>
+        <v>132586355</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,45 +3333,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532091</v>
+        <v>532518</v>
       </c>
       <c r="R25" t="n">
-        <v>6921651</v>
+        <v>6921775</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3387,7 +3392,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3397,12 +3402,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132586316</v>
+        <v>132586351</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3691,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532580</v>
+        <v>532556</v>
       </c>
       <c r="R28" t="n">
-        <v>6921193</v>
+        <v>6921736</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,10 +3763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132586349</v>
+        <v>132586338</v>
       </c>
       <c r="B29" t="n">
-        <v>58119</v>
+        <v>92217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,49 +3774,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>532533</v>
+        <v>532424</v>
       </c>
       <c r="R29" t="n">
-        <v>6921722</v>
+        <v>6921684</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3845,7 +3833,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3855,7 +3843,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3882,10 +3870,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132586351</v>
+        <v>132586316</v>
       </c>
       <c r="B30" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3893,21 +3881,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3917,13 +3905,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532556</v>
+        <v>532580</v>
       </c>
       <c r="R30" t="n">
-        <v>6921736</v>
+        <v>6921193</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3952,7 +3940,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3962,7 +3950,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,10 +3977,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132586338</v>
+        <v>132586348</v>
       </c>
       <c r="B31" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4000,21 +3988,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4024,10 +4012,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532424</v>
+        <v>532526</v>
       </c>
       <c r="R31" t="n">
-        <v>6921684</v>
+        <v>6921737</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4059,7 +4047,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4069,7 +4057,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,10 +4084,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132586348</v>
+        <v>132586349</v>
       </c>
       <c r="B32" t="n">
-        <v>80438</v>
+        <v>58119</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4107,37 +4095,49 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532526</v>
+        <v>532533</v>
       </c>
       <c r="R32" t="n">
-        <v>6921737</v>
+        <v>6921722</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4555,32 +4555,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132586343</v>
+        <v>132586352</v>
       </c>
       <c r="B36" t="n">
-        <v>83181</v>
+        <v>92342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>4217</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532452</v>
+        <v>532543</v>
       </c>
       <c r="R36" t="n">
-        <v>6921716</v>
+        <v>6921755</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,32 +4662,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132586352</v>
+        <v>132586343</v>
       </c>
       <c r="B37" t="n">
-        <v>92342</v>
+        <v>83181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532543</v>
+        <v>532452</v>
       </c>
       <c r="R37" t="n">
-        <v>6921755</v>
+        <v>6921716</v>
       </c>
       <c r="S37" t="n">
         <v>6</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4769,10 +4769,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132586341</v>
+        <v>132586372</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,37 +4780,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>532433</v>
+        <v>532266</v>
       </c>
       <c r="R38" t="n">
-        <v>6921710</v>
+        <v>6921577</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4839,7 +4847,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4849,7 +4857,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4876,7 +4889,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132586372</v>
+        <v>132586374</v>
       </c>
       <c r="B39" t="n">
         <v>57958</v>
@@ -4919,10 +4932,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532266</v>
+        <v>532212</v>
       </c>
       <c r="R39" t="n">
-        <v>6921577</v>
+        <v>6921515</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4954,7 +4967,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4964,12 +4977,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4996,10 +5009,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132586374</v>
+        <v>132586341</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5007,45 +5020,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532212</v>
+        <v>532433</v>
       </c>
       <c r="R40" t="n">
-        <v>6921515</v>
+        <v>6921710</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5074,7 +5079,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5084,12 +5089,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5776,7 +5776,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132586329</v>
+        <v>132586337</v>
       </c>
       <c r="B47" t="n">
         <v>99130</v>
@@ -5811,13 +5811,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532354</v>
+        <v>532410</v>
       </c>
       <c r="R47" t="n">
-        <v>6921519</v>
+        <v>6921666</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5888,7 +5888,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132586337</v>
+        <v>132586329</v>
       </c>
       <c r="B48" t="n">
         <v>99130</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532410</v>
+        <v>532354</v>
       </c>
       <c r="R48" t="n">
-        <v>6921666</v>
+        <v>6921519</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,10 +6214,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132586346</v>
+        <v>132586324</v>
       </c>
       <c r="B51" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532520</v>
+        <v>532330</v>
       </c>
       <c r="R51" t="n">
-        <v>6921725</v>
+        <v>6921453</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132586347</v>
+        <v>132586346</v>
       </c>
       <c r="B52" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6356,13 +6356,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532521</v>
+        <v>532520</v>
       </c>
       <c r="R52" t="n">
-        <v>6921732</v>
+        <v>6921725</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6428,32 +6428,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132586324</v>
+        <v>132586347</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>80467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532330</v>
+        <v>532521</v>
       </c>
       <c r="R53" t="n">
-        <v>6921453</v>
+        <v>6921732</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7208,10 +7208,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132586315</v>
+        <v>132586375</v>
       </c>
       <c r="B60" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7219,34 +7219,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532561</v>
+        <v>532201</v>
       </c>
       <c r="R60" t="n">
-        <v>6921190</v>
+        <v>6921512</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7278,7 +7286,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7288,7 +7296,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7315,10 +7328,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132586375</v>
+        <v>132586315</v>
       </c>
       <c r="B61" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7326,42 +7339,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532201</v>
+        <v>532561</v>
       </c>
       <c r="R61" t="n">
-        <v>6921512</v>
+        <v>6921190</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7393,7 +7398,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7403,12 +7408,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7542,7 +7542,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132586373</v>
+        <v>132586377</v>
       </c>
       <c r="B63" t="n">
         <v>99130</v>
@@ -7577,13 +7577,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532239</v>
+        <v>532374</v>
       </c>
       <c r="R63" t="n">
-        <v>6921525</v>
+        <v>6921276</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>2 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7654,7 +7654,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132586377</v>
+        <v>132586373</v>
       </c>
       <c r="B64" t="n">
         <v>99130</v>
@@ -7689,13 +7689,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532374</v>
+        <v>532239</v>
       </c>
       <c r="R64" t="n">
-        <v>6921276</v>
+        <v>6921525</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7766,48 +7766,60 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132586356</v>
+        <v>132586320</v>
       </c>
       <c r="B65" t="n">
-        <v>92378</v>
+        <v>57145</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532498</v>
+        <v>532436</v>
       </c>
       <c r="R65" t="n">
-        <v>6921779</v>
+        <v>6921359</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7836,7 +7848,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7846,7 +7858,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7873,45 +7885,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132586333</v>
+        <v>132586366</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532453</v>
+        <v>532089</v>
       </c>
       <c r="R66" t="n">
-        <v>6921617</v>
+        <v>6921665</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7943,7 +7963,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7953,7 +7973,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7980,56 +8005,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132586366</v>
+        <v>132586356</v>
       </c>
       <c r="B67" t="n">
-        <v>57958</v>
+        <v>92378</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532089</v>
+        <v>532498</v>
       </c>
       <c r="R67" t="n">
-        <v>6921665</v>
+        <v>6921779</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8058,7 +8075,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8068,12 +8085,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8207,10 +8219,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132586320</v>
+        <v>132586333</v>
       </c>
       <c r="B69" t="n">
-        <v>57145</v>
+        <v>91881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8218,46 +8230,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532436</v>
+        <v>532453</v>
       </c>
       <c r="R69" t="n">
-        <v>6921359</v>
+        <v>6921617</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 31509-2024 artfynd.xlsx
+++ b/artfynd/A 31509-2024 artfynd.xlsx
@@ -1417,32 +1417,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132586331</v>
+        <v>132586322</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>97243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532456</v>
+        <v>532371</v>
       </c>
       <c r="R8" t="n">
-        <v>6921636</v>
+        <v>6921471</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132586342</v>
+        <v>132586358</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1564,13 +1559,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532450</v>
+        <v>532488</v>
       </c>
       <c r="R9" t="n">
-        <v>6921712</v>
+        <v>6921801</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,12 +1604,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>30 ex</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,32 +1631,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132586322</v>
+        <v>132586345</v>
       </c>
       <c r="B10" t="n">
-        <v>97243</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,13 +1666,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532371</v>
+        <v>532451</v>
       </c>
       <c r="R10" t="n">
-        <v>6921471</v>
+        <v>6921744</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,32 +1738,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132586358</v>
+        <v>132586319</v>
       </c>
       <c r="B11" t="n">
-        <v>80438</v>
+        <v>80466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532488</v>
+        <v>532428</v>
       </c>
       <c r="R11" t="n">
-        <v>6921801</v>
+        <v>6921348</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,32 +1845,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132586345</v>
+        <v>132586331</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1890,13 +1880,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532451</v>
+        <v>532456</v>
       </c>
       <c r="R12" t="n">
-        <v>6921744</v>
+        <v>6921636</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1925,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,32 +1957,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132586319</v>
+        <v>132586342</v>
       </c>
       <c r="B13" t="n">
-        <v>80466</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1997,13 +1992,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532428</v>
+        <v>532450</v>
       </c>
       <c r="R13" t="n">
-        <v>6921348</v>
+        <v>6921712</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2032,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2037,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2640,48 +2640,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132586361</v>
+        <v>132586336</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532468</v>
+        <v>532410</v>
       </c>
       <c r="R19" t="n">
-        <v>6921825</v>
+        <v>6921645</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2710,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,12 +2732,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Kunde inte se med kikaren om det var både en hane och en hona. Men den ena födosökte uteslutande högt upp i träden, medan den andra var lågt ner på flera stammar. Möjligen utifrån detta att det handlar om en hane och en hona.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,60 +2764,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132586336</v>
+        <v>132586361</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532410</v>
+        <v>532468</v>
       </c>
       <c r="R20" t="n">
-        <v>6921645</v>
+        <v>6921825</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Kunde inte se med kikaren om det var både en hane och en hona. Men den ena födosökte uteslutande högt upp i träden, medan den andra var lågt ner på flera stammar. Möjligen utifrån detta att det handlar om en hane och en hona.</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132586351</v>
+        <v>132586349</v>
       </c>
       <c r="B28" t="n">
-        <v>83181</v>
+        <v>58119</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3667,37 +3667,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532556</v>
+        <v>532533</v>
       </c>
       <c r="R28" t="n">
-        <v>6921736</v>
+        <v>6921722</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3738,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3748,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,10 +3775,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132586338</v>
+        <v>132586351</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>83181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,21 +3786,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3798,13 +3810,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>532424</v>
+        <v>532556</v>
       </c>
       <c r="R29" t="n">
-        <v>6921684</v>
+        <v>6921736</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3833,7 +3845,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3843,7 +3855,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,10 +3882,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132586316</v>
+        <v>132586338</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3881,21 +3893,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3905,13 +3917,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532580</v>
+        <v>532424</v>
       </c>
       <c r="R30" t="n">
-        <v>6921193</v>
+        <v>6921684</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3940,7 +3952,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3950,7 +3962,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3977,32 +3989,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132586348</v>
+        <v>132586326</v>
       </c>
       <c r="B31" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4012,10 +4024,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532526</v>
+        <v>532327</v>
       </c>
       <c r="R31" t="n">
-        <v>6921737</v>
+        <v>6921455</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4047,7 +4059,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4057,7 +4069,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>140 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,10 +4101,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132586349</v>
+        <v>132586316</v>
       </c>
       <c r="B32" t="n">
-        <v>58119</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4095,49 +4112,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532533</v>
+        <v>532580</v>
       </c>
       <c r="R32" t="n">
-        <v>6921722</v>
+        <v>6921193</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4166,7 +4171,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4176,7 +4181,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4203,32 +4208,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132586326</v>
+        <v>132586348</v>
       </c>
       <c r="B33" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4238,10 +4243,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>532327</v>
+        <v>532526</v>
       </c>
       <c r="R33" t="n">
-        <v>6921455</v>
+        <v>6921737</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4273,7 +4278,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4283,12 +4288,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>140 ex</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6861,48 +6861,56 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132586330</v>
+        <v>132586328</v>
       </c>
       <c r="B57" t="n">
-        <v>80342</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532342</v>
+        <v>532350</v>
       </c>
       <c r="R57" t="n">
-        <v>6921556</v>
+        <v>6921513</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6931,7 +6939,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6941,7 +6949,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6968,7 +6981,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132586328</v>
+        <v>132586369</v>
       </c>
       <c r="B58" t="n">
         <v>57958</v>
@@ -7011,13 +7024,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532350</v>
+        <v>532097</v>
       </c>
       <c r="R58" t="n">
-        <v>6921513</v>
+        <v>6921643</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7046,7 +7059,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7056,12 +7069,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7088,53 +7101,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132586369</v>
+        <v>132586330</v>
       </c>
       <c r="B59" t="n">
-        <v>57958</v>
+        <v>80342</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flåmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532097</v>
+        <v>532342</v>
       </c>
       <c r="R59" t="n">
-        <v>6921643</v>
+        <v>6921556</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7166,7 +7171,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7176,12 +7181,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
